--- a/data/trans_bre/P1423-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,98</t>
+          <t>0,29; 6,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,7</t>
+          <t>-0,95; 5,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 5,89</t>
+          <t>-0,4; 5,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,9</t>
+          <t>0,39; 6,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 412,64</t>
+          <t>-0,06; 419,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 315,1</t>
+          <t>-32,2; 323,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 439,97</t>
+          <t>-26,53; 340,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 174,67</t>
+          <t>3,43; 197,79</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,73</t>
+          <t>1,18; 6,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,79</t>
+          <t>-0,58; 5,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,04</t>
+          <t>-0,61; 4,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,36</t>
+          <t>1,11; 7,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,76; 550,87</t>
+          <t>19,99; 594,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 298,56</t>
+          <t>-18,71; 304,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 398,17</t>
+          <t>-22,78; 404,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 193,04</t>
+          <t>12,54; 180,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 12,51</t>
+          <t>2,33; 13,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 12,78</t>
+          <t>3,42; 12,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,89</t>
+          <t>4,7; 16,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 15,59</t>
+          <t>3,63; 14,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,25; 425,98</t>
+          <t>48,77; 469,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,36; 224,32</t>
+          <t>42,58; 244,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,33; 591,07</t>
+          <t>86,21; 560,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43,2; 815,81</t>
+          <t>45,28; 665,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,32</t>
+          <t>2,64; 7,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,05</t>
+          <t>3,49; 8,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,65</t>
+          <t>2,92; 7,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 6,46</t>
+          <t>-2,01; 6,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,0; 287,49</t>
+          <t>67,5; 274,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,74; 246,43</t>
+          <t>58,73; 228,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,11; 283,11</t>
+          <t>68,28; 276,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,55; 121,41</t>
+          <t>-23,91; 122,04</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,8</t>
+          <t>1,19; 7,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 14,64</t>
+          <t>8,46; 14,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 14,32</t>
+          <t>7,81; 14,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 10,54</t>
+          <t>2,35; 10,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,54; 256,22</t>
+          <t>13,51; 252,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>171,93; 691,05</t>
+          <t>173,55; 670,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>132,31; 463,65</t>
+          <t>134,09; 433,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,72; 172,55</t>
+          <t>28,55; 175,75</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,88</t>
+          <t>1,83; 6,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,46; 13,85</t>
+          <t>9,57; 13,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,39</t>
+          <t>7,43; 12,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,4</t>
+          <t>1,32; 10,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,61; 646,24</t>
+          <t>26,42; 503,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>410,04; —</t>
+          <t>408,38; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>216,74; 3170,51</t>
+          <t>221,54; 3109,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 351,77</t>
+          <t>10,72; 368,43</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,5</t>
+          <t>3,31; 5,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 8,63</t>
+          <t>6,12; 8,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,35</t>
+          <t>5,76; 8,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,42</t>
+          <t>3,33; 7,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,62; 207,2</t>
+          <t>90,52; 209,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>126,37; 240,97</t>
+          <t>131,64; 239,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>154,26; 298,32</t>
+          <t>152,99; 290,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60,99; 159,8</t>
+          <t>56,46; 160,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1423-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,01</t>
+          <t>0,18; 5,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,3</t>
+          <t>-0,48; 5,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,6</t>
+          <t>-0,36; 5,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,2</t>
+          <t>1,11; 6,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 419,57</t>
+          <t>-7,86; 417,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 323,24</t>
+          <t>-19,82; 321,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 340,9</t>
+          <t>-17,39; 359,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 197,79</t>
+          <t>16,64; 198,09</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,04</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,98</t>
+          <t>1,07; 6,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 5,83</t>
+          <t>-0,77; 5,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,83</t>
+          <t>-0,66; 4,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,84</t>
+          <t>0,71; 7,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,99; 594,8</t>
+          <t>19,33; 524,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 304,22</t>
+          <t>-26,42; 286,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 404,95</t>
+          <t>-28,93; 370,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 180,72</t>
+          <t>8,13; 168,9</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>5,83</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>172,81%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 13,12</t>
+          <t>2,39; 12,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,92</t>
+          <t>3,6; 13,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 16,71</t>
+          <t>4,33; 17,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 14,57</t>
+          <t>1,55; 10,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,77; 469,81</t>
+          <t>50,56; 478,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,58; 244,51</t>
+          <t>42,99; 232,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,21; 560,42</t>
+          <t>78,35; 538,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45,28; 665,39</t>
+          <t>16,96; 202,57</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,21</t>
+          <t>2,82; 7,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,89</t>
+          <t>3,44; 8,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,43</t>
+          <t>2,82; 7,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 6,55</t>
+          <t>3,29; 8,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,5; 274,81</t>
+          <t>74,01; 280,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,73; 228,24</t>
+          <t>60,04; 236,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,28; 276,31</t>
+          <t>65,44; 259,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 122,04</t>
+          <t>41,04; 156,04</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>146,1%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,82</t>
+          <t>1,01; 7,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 14,73</t>
+          <t>8,59; 14,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 14,1</t>
+          <t>7,97; 14,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 10,61</t>
+          <t>6,8; 12,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,51; 252,38</t>
+          <t>13,2; 254,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>173,55; 670,66</t>
+          <t>173,77; 646,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>134,09; 433,61</t>
+          <t>138,39; 458,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>28,55; 175,75</t>
+          <t>76,1; 242,7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,82</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>123,41%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,73</t>
+          <t>2,1; 6,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,57; 13,96</t>
+          <t>9,5; 14,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,35</t>
+          <t>7,41; 12,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 10,41</t>
+          <t>-0,14; 9,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,42; 503,78</t>
+          <t>37,25; 613,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>408,38; —</t>
+          <t>489,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>221,54; 3109,29</t>
+          <t>166,0; 2935,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,72; 368,43</t>
+          <t>-4,26; 279,07</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>6,27</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>103,5%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,62</t>
+          <t>3,48; 5,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,57</t>
+          <t>6,1; 8,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,25</t>
+          <t>5,67; 8,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,25</t>
+          <t>5,0; 7,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,52; 209,33</t>
+          <t>98,01; 208,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>131,64; 239,56</t>
+          <t>128,5; 236,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>152,99; 290,27</t>
+          <t>149,78; 288,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>56,46; 160,56</t>
+          <t>75,33; 142,4</t>
         </is>
       </c>
     </row>
